--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484613_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484613_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5613</v>
+        <v>7.3572</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2655</v>
+        <v>5.4578</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2957</v>
+        <v>1.8994</v>
       </c>
       <c r="G2" t="n">
         <v>4.7426</v>
@@ -610,13 +610,13 @@
         <v>1.8326</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5517</v>
+        <v>1.3476</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1116</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6633</v>
+        <v>1.2669</v>
       </c>
       <c r="V2" t="n">
         <v>1.267</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5175</v>
+        <v>3.5364</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7145</v>
+        <v>3.9068</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.197</v>
+        <v>-0.3704</v>
       </c>
       <c r="G3" t="n">
         <v>8.475</v>
@@ -688,13 +688,13 @@
         <v>1.8326</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2599</v>
+        <v>1.2788</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2767</v>
+        <v>-0.0844</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5367</v>
+        <v>1.3633</v>
       </c>
       <c r="V3" t="n">
         <v>-3.4686</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8715</v>
+        <v>2.3353</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7875</v>
+        <v>0.499</v>
       </c>
       <c r="F4" t="n">
-        <v>2.084</v>
+        <v>1.8363</v>
       </c>
       <c r="G4" t="n">
         <v>0.9469</v>
@@ -766,13 +766,13 @@
         <v>0.733</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1915</v>
+        <v>0.6553</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2557</v>
+        <v>-0.0328</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9359</v>
+        <v>0.6881</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6017</v>
+        <v>1.1516</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1336</v>
+        <v>0.4605</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4681</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4254</v>
@@ -844,13 +844,13 @@
         <v>0.9163</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7889</v>
+        <v>0.3388</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8416</v>
+        <v>0.1686</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0527</v>
+        <v>0.1702</v>
       </c>
       <c r="V5" t="n">
         <v>0.3219</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0293</v>
+        <v>0.056</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5941</v>
+        <v>1.0171</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5648</v>
+        <v>-0.9611</v>
       </c>
       <c r="G6" t="n">
         <v>1.5513</v>
@@ -922,13 +922,13 @@
         <v>0.9163</v>
       </c>
       <c r="S6" t="n">
-        <v>1.643</v>
+        <v>0.6697</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4193</v>
+        <v>-0.1576</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2236</v>
+        <v>0.8273</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3324</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MONTILLA GONZALEZ</t>
+          <t>J. SEGARRA SARIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6163</v>
+        <v>-0.1519</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7659</v>
+        <v>0.1522</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1497</v>
+        <v>-0.3041</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4174</v>
+        <v>0.1149</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3754</v>
+        <v>-0.1895</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.042</v>
+        <v>0.3045</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4303</v>
+        <v>0.4218</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0552</v>
+        <v>0.2135</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3751</v>
+        <v>0.2084</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8477</v>
+        <v>-0.3069</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4306</v>
+        <v>-0.403</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.417</v>
+        <v>0.0961</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.9321</v>
+        <v>0.1833</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.5814</v>
+        <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6493</v>
+        <v>1.0995</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1443</v>
+        <v>0.1834</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4744</v>
+        <v>0.0132</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.1702</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5889</v>
+        <v>-0.6335</v>
       </c>
       <c r="W7" t="n">
-        <v>1.9109</v>
+        <v>0.6335</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3219</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SEGARRA SARIO</t>
+          <t>J. MONTILLA GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6633</v>
+        <v>-0.8115</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1362</v>
+        <v>-1.8621</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5271</v>
+        <v>1.0506</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1149</v>
+        <v>-0.4174</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1895</v>
+        <v>-0.3754</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3045</v>
+        <v>-0.042</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4218</v>
+        <v>0.4303</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2135</v>
+        <v>0.0552</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2084</v>
+        <v>0.3751</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3069</v>
+        <v>-0.8477</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.403</v>
+        <v>-0.4306</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0961</v>
+        <v>-0.417</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1833</v>
+        <v>-2.9321</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>-4.5814</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.328</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2753</v>
+        <v>0.3782</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0527</v>
+        <v>0.5709</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6335</v>
+        <v>1.5889</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6335</v>
+        <v>1.9109</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8514</v>
+        <v>-0.8761</v>
       </c>
       <c r="E9" t="n">
         <v>-0.8612</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.0149</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8899</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0385</v>
+        <v>0.0138</v>
       </c>
       <c r="T9" t="n">
         <v>-0.2202</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2587</v>
+        <v>0.234</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.525</v>
+        <v>-1.0106</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9156</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6094000000000001</v>
+        <v>-0.2874</v>
       </c>
       <c r="G10" t="n">
         <v>-1.153</v>
@@ -1234,13 +1234,13 @@
         <v>0.5498</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9218</v>
+        <v>-0.4074</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4955</v>
+        <v>-0.3032</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4263</v>
+        <v>-0.1043</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1643</v>
+        <v>-1.191</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1106</v>
+        <v>-0.5337</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0536</v>
+        <v>-0.6573</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9851</v>
@@ -1312,13 +1312,13 @@
         <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1475</v>
+        <v>-0.1742</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9728</v>
+        <v>-0.3959</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1747</v>
+        <v>0.2217</v>
       </c>
       <c r="V11" t="n">
         <v>2.5339</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2922</v>
+        <v>-2.9264</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4096</v>
+        <v>-2.2173</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8316</v>
@@ -1390,13 +1390,13 @@
         <v>0.3665</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9108000000000001</v>
+        <v>-0.5451</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3854</v>
+        <v>-0.1931</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5254</v>
+        <v>-0.352</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.468800000000003</v>
+        <v>7.468999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2961</v>
+        <v>5.2958</v>
       </c>
       <c r="F13" t="n">
         <v>2.1729</v>
@@ -1456,7 +1456,7 @@
         <v>-7.815900000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9636999999999997</v>
+        <v>-0.9636999999999998</v>
       </c>
       <c r="P13" t="n">
         <v>-8.246599999999999</v>
@@ -1468,13 +1468,13 @@
         <v>10.9954</v>
       </c>
       <c r="S13" t="n">
-        <v>4.309699999999999</v>
+        <v>4.3098</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7465000000000002</v>
+        <v>-0.7464999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>5.056299999999999</v>
+        <v>5.0563</v>
       </c>
       <c r="V13" t="n">
         <v>1.2772</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.7056</v>
+        <v>8.224299999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4357</v>
+        <v>4.628</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2699</v>
+        <v>3.5963</v>
       </c>
       <c r="G14" t="n">
         <v>5.4664</v>
@@ -1546,13 +1546,13 @@
         <v>3.4819</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3528</v>
+        <v>-0.8341</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2662</v>
+        <v>-1.0739</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0866</v>
+        <v>0.2398</v>
       </c>
       <c r="V14" t="n">
         <v>0.11</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3147</v>
+        <v>2.0194</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5084</v>
+        <v>3.2584</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1937</v>
+        <v>-1.2389</v>
       </c>
       <c r="G15" t="n">
         <v>2.9207</v>
@@ -1624,13 +1624,13 @@
         <v>3.8484</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0744</v>
+        <v>-0.2208</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8206</v>
+        <v>-0.4294</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2539</v>
+        <v>0.2087</v>
       </c>
       <c r="V15" t="n">
         <v>-1.78</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3233</v>
+        <v>1.7604</v>
       </c>
       <c r="E16" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.3668</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2449</v>
+        <v>1.3936</v>
       </c>
       <c r="G16" t="n">
         <v>0.7845</v>
@@ -1702,13 +1702,13 @@
         <v>1.4661</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9273</v>
+        <v>-0.4902</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5324</v>
+        <v>-0.244</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3949</v>
+        <v>-0.2462</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6304</v>
+        <v>1.05</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5763</v>
+        <v>2.7686</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9459</v>
+        <v>-1.7186</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0709</v>
@@ -1780,13 +1780,13 @@
         <v>3.6651</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2725</v>
+        <v>-0.8529</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1576</v>
+        <v>-0.9653</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.115</v>
+        <v>0.1123</v>
       </c>
       <c r="V17" t="n">
         <v>0.1413</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.416</v>
+        <v>-1.1493</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9497</v>
+        <v>-0.7574</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4663</v>
+        <v>-0.392</v>
       </c>
       <c r="G19" t="n">
         <v>-1.5017</v>
@@ -1936,13 +1936,13 @@
         <v>0.3665</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2808</v>
+        <v>-0.0141</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3303</v>
+        <v>-0.138</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0495</v>
+        <v>0.1239</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8556</v>
+        <v>-1.6137</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2278</v>
+        <v>-0.0355</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6278</v>
+        <v>-1.5782</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2287</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6268</v>
+        <v>-0.385</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2753</v>
+        <v>-0.083</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3516</v>
+        <v>-0.302</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2441</v>
+        <v>-2.9236</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.338</v>
+        <v>-2.1457</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9061</v>
+        <v>-0.7779</v>
       </c>
       <c r="G21" t="n">
         <v>-4.4322</v>
@@ -2092,13 +2092,13 @@
         <v>2.1991</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8982</v>
+        <v>-0.5777</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2111</v>
+        <v>-1.0188</v>
       </c>
       <c r="U21" t="n">
-        <v>0.313</v>
+        <v>0.4412</v>
       </c>
       <c r="V21" t="n">
         <v>1.7198</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. MAS VIDAL</t>
+          <t>J. CHALER ROMERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4017</v>
+        <v>-3.8282</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5415</v>
+        <v>-4.2706</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8601</v>
+        <v>0.4424</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.8171</v>
+        <v>-4.9594</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.6563</v>
+        <v>-0.6322</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1608</v>
+        <v>-4.3272</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0386</v>
+        <v>-3.6511</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2886</v>
+        <v>0.1951</v>
       </c>
       <c r="L22" t="n">
-        <v>0.25</v>
+        <v>-3.8462</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7786</v>
+        <v>-1.3083</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3677</v>
+        <v>-0.8273</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4109</v>
+        <v>-0.481</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1833</v>
+        <v>1.2828</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.5656</v>
+        <v>1.2828</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1667</v>
+        <v>-0.1516</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0211</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1878</v>
+        <v>0.4679</v>
       </c>
       <c r="V22" t="n">
-        <v>0.432</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.835</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. CHALER ROMERO</t>
+          <t>V. MAS VIDAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8748</v>
+        <v>-3.9306</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3668</v>
+        <v>-2.9261</v>
       </c>
       <c r="F23" t="n">
-        <v>0.492</v>
+        <v>-1.0044</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.9594</v>
+        <v>-3.8171</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6322</v>
+        <v>-2.6563</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.3272</v>
+        <v>-1.1608</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.6511</v>
+        <v>-1.0386</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1951</v>
+        <v>-1.2886</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.8462</v>
+        <v>0.25</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3083</v>
+        <v>-2.7786</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8273</v>
+        <v>-1.3677</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.481</v>
+        <v>-1.4109</v>
       </c>
       <c r="P23" t="n">
-        <v>1.2828</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2828</v>
+        <v>2.5656</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1982</v>
+        <v>-0.3622</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7157</v>
+        <v>-0.4057</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5175</v>
+        <v>0.0435</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.432</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.835</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2758</v>
+        <v>-7.0617</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9729</v>
+        <v>-3.6844</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.303</v>
+        <v>-3.3773</v>
       </c>
       <c r="G24" t="n">
         <v>-3.9148</v>
@@ -2326,13 +2326,13 @@
         <v>0.3665</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0055</v>
+        <v>0.2196</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3673</v>
+        <v>-0.0788</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3728</v>
+        <v>0.2984</v>
       </c>
       <c r="V24" t="n">
         <v>-1.9005</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.468900000000001</v>
+        <v>-6.827900000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.172900000000002</v>
+        <v>-2.172799999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.2961</v>
+        <v>-4.654999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-10.1281</v>
@@ -2404,13 +2404,13 @@
         <v>19.242</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.31</v>
+        <v>-3.669</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.0564</v>
+        <v>-5.056400000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7464</v>
+        <v>1.3875</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2774</v>
